--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/147.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/147.xlsx
@@ -426,13 +426,13 @@
         <v>-12.57600854906028</v>
       </c>
       <c r="E2">
-        <v>-11.53663830374643</v>
+        <v>-8.385427209924888</v>
       </c>
       <c r="F2">
-        <v>-3.928511845839093</v>
+        <v>-4.192042024426505</v>
       </c>
       <c r="G2">
-        <v>-14.68634136262887</v>
+        <v>-14.49868502042267</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.94855464124798</v>
       </c>
       <c r="E3">
-        <v>-12.15012879146156</v>
+        <v>-9.113732627630496</v>
       </c>
       <c r="F3">
-        <v>-3.980270726268214</v>
+        <v>-3.905987707789572</v>
       </c>
       <c r="G3">
-        <v>-15.40615934223206</v>
+        <v>-14.11649161440011</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.24442125681623</v>
       </c>
       <c r="E4">
-        <v>-12.308611796308</v>
+        <v>-9.735655133947912</v>
       </c>
       <c r="F4">
-        <v>-3.883854559154172</v>
+        <v>-3.817711078775437</v>
       </c>
       <c r="G4">
-        <v>-14.78145085075094</v>
+        <v>-14.29555771856369</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.36694519330024</v>
       </c>
       <c r="E5">
-        <v>-13.83856126827344</v>
+        <v>-10.08437933185658</v>
       </c>
       <c r="F5">
-        <v>-3.977148609527063</v>
+        <v>-3.770878499290764</v>
       </c>
       <c r="G5">
-        <v>-15.01565952383176</v>
+        <v>-14.64832677025193</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.31858331464066</v>
       </c>
       <c r="E6">
-        <v>-13.74659248965166</v>
+        <v>-10.24743156697676</v>
       </c>
       <c r="F6">
-        <v>-3.788285811893193</v>
+        <v>-3.700946894779027</v>
       </c>
       <c r="G6">
-        <v>-14.84311648812836</v>
+        <v>-14.3090353361191</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.07579192936519</v>
       </c>
       <c r="E7">
-        <v>-15.17744083643324</v>
+        <v>-11.58994297129072</v>
       </c>
       <c r="F7">
-        <v>-3.340357735972999</v>
+        <v>-3.530497876141987</v>
       </c>
       <c r="G7">
-        <v>-15.54803936246245</v>
+        <v>-14.22721807653435</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.66498551093591</v>
       </c>
       <c r="E8">
-        <v>-15.1437625752382</v>
+        <v>-12.3887250299777</v>
       </c>
       <c r="F8">
-        <v>-3.578364258145353</v>
+        <v>-3.384948753265697</v>
       </c>
       <c r="G8">
-        <v>-15.44058427822297</v>
+        <v>-13.89509611150891</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.09911118085768</v>
       </c>
       <c r="E9">
-        <v>-15.96119741836277</v>
+        <v>-12.385953603885</v>
       </c>
       <c r="F9">
-        <v>-3.312335723471098</v>
+        <v>-3.221806763488751</v>
       </c>
       <c r="G9">
-        <v>-14.76881158530396</v>
+        <v>-13.60076725640516</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.43074701590287</v>
       </c>
       <c r="E10">
-        <v>-16.08963852664233</v>
+        <v>-14.39099434094315</v>
       </c>
       <c r="F10">
-        <v>-3.271115333140391</v>
+        <v>-3.010896139061969</v>
       </c>
       <c r="G10">
-        <v>-14.5387717042144</v>
+        <v>-12.79841014847415</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.69496953092395</v>
       </c>
       <c r="E11">
-        <v>-16.65329768637706</v>
+        <v>-15.37130480870161</v>
       </c>
       <c r="F11">
-        <v>-3.257243492613111</v>
+        <v>-3.53596427263306</v>
       </c>
       <c r="G11">
-        <v>-14.15554143217906</v>
+        <v>-13.64360032264216</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.956698688443003</v>
       </c>
       <c r="E12">
-        <v>-16.7840936011406</v>
+        <v>-14.49828294713288</v>
       </c>
       <c r="F12">
-        <v>-3.118194568746589</v>
+        <v>-3.106339802845125</v>
       </c>
       <c r="G12">
-        <v>-13.85266007308062</v>
+        <v>-12.42606368835148</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.259180759040648</v>
       </c>
       <c r="E13">
-        <v>-18.00201310008152</v>
+        <v>-15.72142830507865</v>
       </c>
       <c r="F13">
-        <v>-2.921738955498658</v>
+        <v>-2.602578107241439</v>
       </c>
       <c r="G13">
-        <v>-13.26463235741253</v>
+        <v>-11.9705054494813</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.666321894232381</v>
       </c>
       <c r="E14">
-        <v>-19.26131832297854</v>
+        <v>-16.97440724978696</v>
       </c>
       <c r="F14">
-        <v>-2.661364856715912</v>
+        <v>-2.60204878047105</v>
       </c>
       <c r="G14">
-        <v>-13.13417755065213</v>
+        <v>-11.6551931825049</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.213392376001869</v>
       </c>
       <c r="E15">
-        <v>-19.47371281088629</v>
+        <v>-17.88772800154995</v>
       </c>
       <c r="F15">
-        <v>-2.169718862745571</v>
+        <v>-2.257843072157591</v>
       </c>
       <c r="G15">
-        <v>-12.47337890323867</v>
+        <v>-11.41897147999735</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.937542617267421</v>
       </c>
       <c r="E16">
-        <v>-19.75811003551601</v>
+        <v>-16.86441514461465</v>
       </c>
       <c r="F16">
-        <v>-2.061145575628043</v>
+        <v>-2.459065111441231</v>
       </c>
       <c r="G16">
-        <v>-12.42958772030632</v>
+        <v>-10.59625767351154</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.84137169259613</v>
       </c>
       <c r="E17">
-        <v>-21.2238593314747</v>
+        <v>-18.31805982955084</v>
       </c>
       <c r="F17">
-        <v>-1.797093525576867</v>
+        <v>-1.540257383971478</v>
       </c>
       <c r="G17">
-        <v>-11.66766510565235</v>
+        <v>-9.886558981197684</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.918623760020042</v>
       </c>
       <c r="E18">
-        <v>-21.24606243953431</v>
+        <v>-19.3552841586377</v>
       </c>
       <c r="F18">
-        <v>-1.683929426313024</v>
+        <v>-1.153943275471512</v>
       </c>
       <c r="G18">
-        <v>-11.35054816681825</v>
+        <v>-9.940193828808367</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.137097339502541</v>
       </c>
       <c r="E19">
-        <v>-22.28533363887264</v>
+        <v>-20.72188251619845</v>
       </c>
       <c r="F19">
-        <v>-1.115542647779935</v>
+        <v>-1.358656054990548</v>
       </c>
       <c r="G19">
-        <v>-11.15248707104705</v>
+        <v>-9.47453927119977</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.455997071367603</v>
       </c>
       <c r="E20">
-        <v>-22.2030693800493</v>
+        <v>-20.74588795691311</v>
       </c>
       <c r="F20">
-        <v>-0.6124146532393907</v>
+        <v>-0.8828318784136781</v>
       </c>
       <c r="G20">
-        <v>-11.32688399693154</v>
+        <v>-8.900463309602442</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.822470239223939</v>
       </c>
       <c r="E21">
-        <v>-23.64197841056453</v>
+        <v>-20.78601476509508</v>
       </c>
       <c r="F21">
-        <v>-0.6229216653764996</v>
+        <v>-0.6402469696060512</v>
       </c>
       <c r="G21">
-        <v>-11.18162759971648</v>
+        <v>-9.303187318922449</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.180360887275318</v>
       </c>
       <c r="E22">
-        <v>-24.01648321099887</v>
+        <v>-20.42415346409016</v>
       </c>
       <c r="F22">
-        <v>-0.1156874536202783</v>
+        <v>-0.3215930821993458</v>
       </c>
       <c r="G22">
-        <v>-11.00441538573399</v>
+        <v>-9.624208911412282</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.479646698509372</v>
       </c>
       <c r="E23">
-        <v>-24.73564563968299</v>
+        <v>-22.17754690054207</v>
       </c>
       <c r="F23">
-        <v>-0.1127649734232017</v>
+        <v>-0.01965647734853722</v>
       </c>
       <c r="G23">
-        <v>-10.50124662203626</v>
+        <v>-8.887164518622013</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.675847493954565</v>
       </c>
       <c r="E24">
-        <v>-24.97014360922218</v>
+        <v>-22.71262233234038</v>
       </c>
       <c r="F24">
-        <v>0.00388406750421913</v>
+        <v>0.6975804681609979</v>
       </c>
       <c r="G24">
-        <v>-10.82309508235907</v>
+        <v>-10.52262378049604</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.746442628743168</v>
       </c>
       <c r="E25">
-        <v>-25.31656734233496</v>
+        <v>-21.6304574272014</v>
       </c>
       <c r="F25">
-        <v>0.2808859851633598</v>
+        <v>0.3163765581689018</v>
       </c>
       <c r="G25">
-        <v>-11.03926195869529</v>
+        <v>-10.45452530825133</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.676805982308871</v>
       </c>
       <c r="E26">
-        <v>-25.72264919202478</v>
+        <v>-23.02806677476668</v>
       </c>
       <c r="F26">
-        <v>0.4152339240189948</v>
+        <v>0.5168356710745626</v>
       </c>
       <c r="G26">
-        <v>-10.31167404643934</v>
+        <v>-10.37032260059286</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.477349643669436</v>
       </c>
       <c r="E27">
-        <v>-25.11259581608147</v>
+        <v>-23.79824699162122</v>
       </c>
       <c r="F27">
-        <v>0.5631016472557205</v>
+        <v>-0.2122071666596711</v>
       </c>
       <c r="G27">
-        <v>-10.97829029967769</v>
+        <v>-10.1473143773052</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.159172282040473</v>
       </c>
       <c r="E28">
-        <v>-25.32238190296081</v>
+        <v>-24.24060191811248</v>
       </c>
       <c r="F28">
-        <v>0.3925780755524284</v>
+        <v>0.5159907363237071</v>
       </c>
       <c r="G28">
-        <v>-11.72407914792388</v>
+        <v>-10.01879221004331</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.75611646810089</v>
       </c>
       <c r="E29">
-        <v>-25.59081172823948</v>
+        <v>-23.5405315358447</v>
       </c>
       <c r="F29">
-        <v>0.269572971543327</v>
+        <v>0.3524693542762791</v>
       </c>
       <c r="G29">
-        <v>-10.92467513939636</v>
+        <v>-10.35678756166015</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.297037652828724</v>
       </c>
       <c r="E30">
-        <v>-25.03466530688347</v>
+        <v>-22.65248872599253</v>
       </c>
       <c r="F30">
-        <v>0.4540404517379433</v>
+        <v>0.8768342039223941</v>
       </c>
       <c r="G30">
-        <v>-10.92187953862772</v>
+        <v>-10.22304825211874</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.82902040236962</v>
       </c>
       <c r="E31">
-        <v>-25.39709719561336</v>
+        <v>-21.92165641979064</v>
       </c>
       <c r="F31">
-        <v>0.4831989843164859</v>
+        <v>0.2734679550712902</v>
       </c>
       <c r="G31">
-        <v>-11.57320201817749</v>
+        <v>-9.972569641935408</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.382909290742598</v>
       </c>
       <c r="E32">
-        <v>-25.25526538969313</v>
+        <v>-22.71654399083102</v>
       </c>
       <c r="F32">
-        <v>0.3972533811738287</v>
+        <v>0.9003383006094273</v>
       </c>
       <c r="G32">
-        <v>-11.29897064512534</v>
+        <v>-9.612970727571184</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.999539784741856</v>
       </c>
       <c r="E33">
-        <v>-24.48749432101067</v>
+        <v>-22.56772022104294</v>
       </c>
       <c r="F33">
-        <v>0.3263782661903031</v>
+        <v>0.6992935319499873</v>
       </c>
       <c r="G33">
-        <v>-10.85500168080311</v>
+        <v>-10.59308473226356</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.694385705473954</v>
       </c>
       <c r="E34">
-        <v>-25.44731344388441</v>
+        <v>-22.36747110042376</v>
       </c>
       <c r="F34">
-        <v>0.01252062604580678</v>
+        <v>0.3914771752741078</v>
       </c>
       <c r="G34">
-        <v>-10.90473843720118</v>
+        <v>-9.138220623799805</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.491137633239103</v>
       </c>
       <c r="E35">
-        <v>-24.15622286192756</v>
+        <v>-22.49201319258271</v>
       </c>
       <c r="F35">
-        <v>-0.2036907213914894</v>
+        <v>0.2461765626186577</v>
       </c>
       <c r="G35">
-        <v>-11.66216249709716</v>
+        <v>-9.977957407736017</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.385535039301103</v>
       </c>
       <c r="E36">
-        <v>-24.16300198751704</v>
+        <v>-20.47191527944906</v>
       </c>
       <c r="F36">
-        <v>0.1045978047039858</v>
+        <v>0.6096666640692892</v>
       </c>
       <c r="G36">
-        <v>-10.68066709812826</v>
+        <v>-9.584073009297153</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.382581995119672</v>
       </c>
       <c r="E37">
-        <v>-23.27966879063285</v>
+        <v>-22.1254966202979</v>
       </c>
       <c r="F37">
-        <v>0.2335712958502577</v>
+        <v>0.355366155083869</v>
       </c>
       <c r="G37">
-        <v>-10.95297239412501</v>
+        <v>-8.925882933023461</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.460285149028436</v>
       </c>
       <c r="E38">
-        <v>-23.66959757353731</v>
+        <v>-21.43280765066262</v>
       </c>
       <c r="F38">
-        <v>-0.1295476970039196</v>
+        <v>0.3364048252337883</v>
       </c>
       <c r="G38">
-        <v>-10.83093720188615</v>
+        <v>-8.542849534281681</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.611609812124913</v>
       </c>
       <c r="E39">
-        <v>-23.58344335554138</v>
+        <v>-20.80514303930348</v>
       </c>
       <c r="F39">
-        <v>0.1475842743374606</v>
+        <v>0.6406865382019222</v>
       </c>
       <c r="G39">
-        <v>-10.92163672823232</v>
+        <v>-8.529239027253105</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.808791202472855</v>
       </c>
       <c r="E40">
-        <v>-23.58615138299797</v>
+        <v>-20.53266928673596</v>
       </c>
       <c r="F40">
-        <v>0.1462746254736345</v>
+        <v>0.3137373796235826</v>
       </c>
       <c r="G40">
-        <v>-10.7651552720624</v>
+        <v>-9.763854419760689</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.041656285429919</v>
       </c>
       <c r="E41">
-        <v>-21.02562085331493</v>
+        <v>-19.99576887991256</v>
       </c>
       <c r="F41">
-        <v>0.1838029822900633</v>
+        <v>0.09930785046970818</v>
       </c>
       <c r="G41">
-        <v>-10.42053185289548</v>
+        <v>-8.12939921168385</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.283558364906412</v>
       </c>
       <c r="E42">
-        <v>-22.23429320833218</v>
+        <v>-18.86130009998499</v>
       </c>
       <c r="F42">
-        <v>0.1889827636597687</v>
+        <v>0.2774366632981027</v>
       </c>
       <c r="G42">
-        <v>-10.28660223250362</v>
+        <v>-8.532805715088221</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.526446869274828</v>
       </c>
       <c r="E43">
-        <v>-21.23920180141269</v>
+        <v>-19.43065608002136</v>
       </c>
       <c r="F43">
-        <v>-0.04550982398990979</v>
+        <v>0.4223661673570986</v>
       </c>
       <c r="G43">
-        <v>-10.60418510479916</v>
+        <v>-8.730154785781023</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.749758602009727</v>
       </c>
       <c r="E44">
-        <v>-20.76857108321753</v>
+        <v>-18.58149927647306</v>
       </c>
       <c r="F44">
-        <v>-0.1465176316176703</v>
+        <v>0.1475975282159054</v>
       </c>
       <c r="G44">
-        <v>-10.05966638700931</v>
+        <v>-7.877978890912958</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.950754493414933</v>
       </c>
       <c r="E45">
-        <v>-21.27957767566508</v>
+        <v>-18.38632657521647</v>
       </c>
       <c r="F45">
-        <v>-0.5171300359975719</v>
+        <v>-0.4840177058054673</v>
       </c>
       <c r="G45">
-        <v>-10.15097950178709</v>
+        <v>-7.711486427765173</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.116673466722375</v>
       </c>
       <c r="E46">
-        <v>-20.52697699490832</v>
+        <v>-18.92896003013359</v>
       </c>
       <c r="F46">
-        <v>-0.1558458769405955</v>
+        <v>0.263528374605099</v>
       </c>
       <c r="G46">
-        <v>-9.920942901919105</v>
+        <v>-8.195286140597499</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.250379770721004</v>
       </c>
       <c r="E47">
-        <v>-19.70040369123626</v>
+        <v>-18.01255085909737</v>
       </c>
       <c r="F47">
-        <v>-0.2869317049640061</v>
+        <v>-0.499975375452997</v>
       </c>
       <c r="G47">
-        <v>-9.58350535796737</v>
+        <v>-7.621761424222158</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.347417814186167</v>
       </c>
       <c r="E48">
-        <v>-19.39850391456691</v>
+        <v>-18.53106566144963</v>
       </c>
       <c r="F48">
-        <v>-0.4669268295509079</v>
+        <v>-0.3301542593072787</v>
       </c>
       <c r="G48">
-        <v>-10.00945713470669</v>
+        <v>-8.193031941386161</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.415438962693655</v>
       </c>
       <c r="E49">
-        <v>-18.48125244736526</v>
+        <v>-18.01366486370326</v>
       </c>
       <c r="F49">
-        <v>-0.5355239341767349</v>
+        <v>-0.6079911713084413</v>
       </c>
       <c r="G49">
-        <v>-10.19040994126694</v>
+        <v>-7.276147076144286</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.457350827905112</v>
       </c>
       <c r="E50">
-        <v>-19.16792760351835</v>
+        <v>-16.67803673988096</v>
       </c>
       <c r="F50">
-        <v>-0.8894936090669917</v>
+        <v>-0.4098473452936052</v>
       </c>
       <c r="G50">
-        <v>-10.14720281577218</v>
+        <v>-7.101579526738709</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.483313921697885</v>
       </c>
       <c r="E51">
-        <v>-18.32823078217207</v>
+        <v>-16.49759969304533</v>
       </c>
       <c r="F51">
-        <v>-0.6429963210159428</v>
+        <v>-0.4132221140926103</v>
       </c>
       <c r="G51">
-        <v>-9.996056625857914</v>
+        <v>-7.783351742360132</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.500835026328971</v>
       </c>
       <c r="E52">
-        <v>-18.74500888746801</v>
+        <v>-15.36094818864607</v>
       </c>
       <c r="F52">
-        <v>-0.826633777072954</v>
+        <v>-0.9401863806487102</v>
       </c>
       <c r="G52">
-        <v>-9.396629946492315</v>
+        <v>-7.369829232887993</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.518723788419786</v>
       </c>
       <c r="E53">
-        <v>-18.34941045510594</v>
+        <v>-15.25979113626273</v>
       </c>
       <c r="F53">
-        <v>-1.01117498196642</v>
+        <v>-1.029602014841694</v>
       </c>
       <c r="G53">
-        <v>-9.883294165746037</v>
+        <v>-7.354876706241603</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.545197228231926</v>
       </c>
       <c r="E54">
-        <v>-18.23844019954798</v>
+        <v>-16.67069608351453</v>
       </c>
       <c r="F54">
-        <v>-0.786015609844083</v>
+        <v>-1.109025053054708</v>
       </c>
       <c r="G54">
-        <v>-9.698531860955264</v>
+        <v>-7.511358162411521</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.583753209446428</v>
       </c>
       <c r="E55">
-        <v>-17.85588830080201</v>
+        <v>-16.18322397048484</v>
       </c>
       <c r="F55">
-        <v>-0.9785737544618421</v>
+        <v>-1.243196549653547</v>
       </c>
       <c r="G55">
-        <v>-9.924299591574417</v>
+        <v>-7.283414981898456</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.640275266485496</v>
       </c>
       <c r="E56">
-        <v>-17.61884532887051</v>
+        <v>-14.43970260736966</v>
       </c>
       <c r="F56">
-        <v>-0.9262830621601233</v>
+        <v>-0.4979491887857493</v>
       </c>
       <c r="G56">
-        <v>-9.899293402069889</v>
+        <v>-7.417466007488011</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.711023941711545</v>
       </c>
       <c r="E57">
-        <v>-16.71149763432364</v>
+        <v>-15.7424766522663</v>
       </c>
       <c r="F57">
-        <v>-0.8355014501199227</v>
+        <v>-1.059096864585774</v>
       </c>
       <c r="G57">
-        <v>-9.85992858702123</v>
+        <v>-8.085686778068927</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.798915632199726</v>
       </c>
       <c r="E58">
-        <v>-16.62311993558994</v>
+        <v>-14.84831134555576</v>
       </c>
       <c r="F58">
-        <v>-0.8163976410765605</v>
+        <v>-1.252416278846705</v>
       </c>
       <c r="G58">
-        <v>-9.722986805237806</v>
+        <v>-7.949722800310217</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.893075385356145</v>
       </c>
       <c r="E59">
-        <v>-16.55196855198142</v>
+        <v>-15.85244158659456</v>
       </c>
       <c r="F59">
-        <v>-0.9786590763043305</v>
+        <v>-0.8511228026019158</v>
       </c>
       <c r="G59">
-        <v>-9.846354173429807</v>
+        <v>-7.371171252505805</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.995701081225265</v>
       </c>
       <c r="E60">
-        <v>-16.21842379894646</v>
+        <v>-14.68715201257079</v>
       </c>
       <c r="F60">
-        <v>-0.8114116976791103</v>
+        <v>-0.7343022896221155</v>
       </c>
       <c r="G60">
-        <v>-9.705743985942924</v>
+        <v>-8.000128925906406</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.092931384975888</v>
       </c>
       <c r="E61">
-        <v>-16.63820428250949</v>
+        <v>-13.88369204023388</v>
       </c>
       <c r="F61">
-        <v>-0.9201390611335594</v>
+        <v>-0.9895214580572403</v>
       </c>
       <c r="G61">
-        <v>-10.23541189495473</v>
+        <v>-7.980645032286423</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.189752154512814</v>
       </c>
       <c r="E62">
-        <v>-15.99235784800955</v>
+        <v>-13.50826795957599</v>
       </c>
       <c r="F62">
-        <v>-0.8302893624215082</v>
+        <v>-0.6993915737985331</v>
       </c>
       <c r="G62">
-        <v>-10.26862770080099</v>
+        <v>-7.853609258390962</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.274492275775104</v>
       </c>
       <c r="E63">
-        <v>-15.44859680306453</v>
+        <v>-13.09104153535329</v>
       </c>
       <c r="F63">
-        <v>-0.847634547468727</v>
+        <v>-1.061707878639398</v>
       </c>
       <c r="G63">
-        <v>-10.43173394329942</v>
+        <v>-7.778019757326034</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.3568888449089</v>
       </c>
       <c r="E64">
-        <v>-15.35847111336387</v>
+        <v>-13.9488205534122</v>
       </c>
       <c r="F64">
-        <v>-0.8357872368738886</v>
+        <v>-0.7185028381485206</v>
       </c>
       <c r="G64">
-        <v>-10.40265247661807</v>
+        <v>-9.221770368367947</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.429366444161897</v>
       </c>
       <c r="E65">
-        <v>-14.83237111704876</v>
+        <v>-15.73090640117671</v>
       </c>
       <c r="F65">
-        <v>-0.9100387773912251</v>
+        <v>-0.7267127874776664</v>
       </c>
       <c r="G65">
-        <v>-10.56286468170107</v>
+        <v>-8.846283779212891</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.505856563242322</v>
       </c>
       <c r="E66">
-        <v>-15.87703572893022</v>
+        <v>-13.90004888834959</v>
       </c>
       <c r="F66">
-        <v>-1.342674362688337</v>
+        <v>-0.9166541194699819</v>
       </c>
       <c r="G66">
-        <v>-10.9762428174246</v>
+        <v>-8.138960691308071</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.579797778306801</v>
       </c>
       <c r="E67">
-        <v>-14.82051104362267</v>
+        <v>-14.31503371793849</v>
       </c>
       <c r="F67">
-        <v>-0.8279749038980864</v>
+        <v>-0.944517085430546</v>
       </c>
       <c r="G67">
-        <v>-10.64474756571702</v>
+        <v>-8.740001731680916</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.663943409303016</v>
       </c>
       <c r="E68">
-        <v>-14.47052792993987</v>
+        <v>-13.32786261205841</v>
       </c>
       <c r="F68">
-        <v>-0.8254873165874795</v>
+        <v>-0.6842788389018589</v>
       </c>
       <c r="G68">
-        <v>-10.63284001267779</v>
+        <v>-9.558869946499058</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.748582888274283</v>
       </c>
       <c r="E69">
-        <v>-14.79917287409853</v>
+        <v>-12.6007345975948</v>
       </c>
       <c r="F69">
-        <v>-0.9569997538233318</v>
+        <v>-0.8325483203289424</v>
       </c>
       <c r="G69">
-        <v>-10.82404335538975</v>
+        <v>-8.54947103938864</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.844229533913254</v>
       </c>
       <c r="E70">
-        <v>-15.84901353177076</v>
+        <v>-13.7758419032672</v>
       </c>
       <c r="F70">
-        <v>-1.009682263906575</v>
+        <v>-1.520251482826467</v>
       </c>
       <c r="G70">
-        <v>-10.99500156107994</v>
+        <v>-9.386743625933708</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.939250526792703</v>
       </c>
       <c r="E71">
-        <v>-15.80430843636703</v>
+        <v>-14.21324267919408</v>
       </c>
       <c r="F71">
-        <v>-1.111408266072562</v>
+        <v>-1.005839467524988</v>
       </c>
       <c r="G71">
-        <v>-10.80984550970203</v>
+        <v>-8.829661110792744</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.04273797910558</v>
       </c>
       <c r="E72">
-        <v>-15.95392016063245</v>
+        <v>-13.19338957640064</v>
       </c>
       <c r="F72">
-        <v>-0.918132755283979</v>
+        <v>-1.542088904299067</v>
       </c>
       <c r="G72">
-        <v>-10.76213654822771</v>
+        <v>-8.928675252570548</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.14266874402863</v>
       </c>
       <c r="E73">
-        <v>-16.04290467488317</v>
+        <v>-14.51759236030159</v>
       </c>
       <c r="F73">
-        <v>-0.9515872012134399</v>
+        <v>-1.027013366707946</v>
       </c>
       <c r="G73">
-        <v>-10.53165698344919</v>
+        <v>-8.56394778890891</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.24763137830396</v>
       </c>
       <c r="E74">
-        <v>-15.91992037778286</v>
+        <v>-13.81532113966608</v>
       </c>
       <c r="F74">
-        <v>-0.9302202924256294</v>
+        <v>-0.7845957881156846</v>
       </c>
       <c r="G74">
-        <v>-9.822726096980247</v>
+        <v>-8.892562128087299</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.34515590031031</v>
       </c>
       <c r="E75">
-        <v>-16.36057712652125</v>
+        <v>-13.7377574368627</v>
       </c>
       <c r="F75">
-        <v>-1.424837640269811</v>
+        <v>-0.977822425227503</v>
       </c>
       <c r="G75">
-        <v>-10.34531641108833</v>
+        <v>-8.655228091471104</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.44296376033703</v>
       </c>
       <c r="E76">
-        <v>-16.18763017569431</v>
+        <v>-15.30162970761959</v>
       </c>
       <c r="F76">
-        <v>-1.024658318181787</v>
+        <v>-1.284853489605529</v>
       </c>
       <c r="G76">
-        <v>-10.19565989576205</v>
+        <v>-9.116256126680883</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.52841238054924</v>
       </c>
       <c r="E77">
-        <v>-16.18521649904822</v>
+        <v>-14.41394917568804</v>
       </c>
       <c r="F77">
-        <v>-1.099879876927802</v>
+        <v>-1.529233470575022</v>
       </c>
       <c r="G77">
-        <v>-9.772251065731309</v>
+        <v>-7.796709595328632</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.60800900248373</v>
       </c>
       <c r="E78">
-        <v>-17.42359564355579</v>
+        <v>-13.8189393903982</v>
       </c>
       <c r="F78">
-        <v>-1.222079807821382</v>
+        <v>-1.259408528093736</v>
       </c>
       <c r="G78">
-        <v>-10.26702318345842</v>
+        <v>-8.07089831250051</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.66886333488726</v>
       </c>
       <c r="E79">
-        <v>-17.45892226928963</v>
+        <v>-16.14610859751798</v>
       </c>
       <c r="F79">
-        <v>-1.289782275652186</v>
+        <v>-1.819107389306264</v>
       </c>
       <c r="G79">
-        <v>-10.13338559178535</v>
+        <v>-8.853046376846907</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.71638288216931</v>
       </c>
       <c r="E80">
-        <v>-17.64003858722641</v>
+        <v>-15.78624888202445</v>
       </c>
       <c r="F80">
-        <v>-1.384810098999137</v>
+        <v>-1.3514517436884</v>
       </c>
       <c r="G80">
-        <v>-9.40836359478889</v>
+        <v>-9.1966362112226</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.73924819583533</v>
       </c>
       <c r="E81">
-        <v>-18.28407363212328</v>
+        <v>-17.63507990818801</v>
       </c>
       <c r="F81">
-        <v>-1.602400678162094</v>
+        <v>-1.907282129129855</v>
       </c>
       <c r="G81">
-        <v>-8.660412421535026</v>
+        <v>-8.598380927953723</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.74272881628681</v>
       </c>
       <c r="E82">
-        <v>-19.19531581431674</v>
+        <v>-16.42105036841967</v>
       </c>
       <c r="F82">
-        <v>-1.76629731064299</v>
+        <v>-1.455356352123751</v>
       </c>
       <c r="G82">
-        <v>-9.243974394660709</v>
+        <v>-7.955861965847937</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.71935911065797</v>
       </c>
       <c r="E83">
-        <v>-19.29124247922122</v>
+        <v>-18.62943770231826</v>
       </c>
       <c r="F83">
-        <v>-1.847175790382723</v>
+        <v>-1.073477322698373</v>
       </c>
       <c r="G83">
-        <v>-9.792814481244349</v>
+        <v>-8.381872804575323</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.6740788484931</v>
       </c>
       <c r="E84">
-        <v>-20.35157108269522</v>
+        <v>-19.66815642782764</v>
       </c>
       <c r="F84">
-        <v>-2.148200362723049</v>
+        <v>-2.051002216780763</v>
       </c>
       <c r="G84">
-        <v>-9.809184495604418</v>
+        <v>-7.450363534843004</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.60518178747216</v>
       </c>
       <c r="E85">
-        <v>-22.30770882894453</v>
+        <v>-19.82612771511122</v>
       </c>
       <c r="F85">
-        <v>-2.200253313580164</v>
+        <v>-1.889747247947395</v>
       </c>
       <c r="G85">
-        <v>-8.849338596484733</v>
+        <v>-7.08804120658444</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.51900464359175</v>
       </c>
       <c r="E86">
-        <v>-22.54398196029474</v>
+        <v>-20.75105494575586</v>
       </c>
       <c r="F86">
-        <v>-1.652310642548167</v>
+        <v>-2.204163207721378</v>
       </c>
       <c r="G86">
-        <v>-9.02639331183237</v>
+        <v>-7.754778865020487</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.42075053532147</v>
       </c>
       <c r="E87">
-        <v>-23.77348076727327</v>
+        <v>-21.8849123816924</v>
       </c>
       <c r="F87">
-        <v>-2.240922011220606</v>
+        <v>-2.103468522971875</v>
       </c>
       <c r="G87">
-        <v>-9.15970606257105</v>
+        <v>-7.299004065527378</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.31770403458264</v>
       </c>
       <c r="E88">
-        <v>-24.67927519523551</v>
+        <v>-22.42640466115958</v>
       </c>
       <c r="F88">
-        <v>-2.083726871028358</v>
+        <v>-2.050712288189783</v>
       </c>
       <c r="G88">
-        <v>-8.651287344378209</v>
+        <v>-7.197368227723579</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.22121217736532</v>
       </c>
       <c r="E89">
-        <v>-26.25657439142515</v>
+        <v>-24.91344258617214</v>
       </c>
       <c r="F89">
-        <v>-1.929524622262424</v>
+        <v>-2.351427051121463</v>
       </c>
       <c r="G89">
-        <v>-8.865629861527378</v>
+        <v>-7.744393798784845</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.13789674033888</v>
       </c>
       <c r="E90">
-        <v>-27.28379984990307</v>
+        <v>-26.22982469546184</v>
       </c>
       <c r="F90">
-        <v>-2.222827153673853</v>
+        <v>-2.256545020437405</v>
       </c>
       <c r="G90">
-        <v>-8.628896288456559</v>
+        <v>-7.699057160497997</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.08318316682514</v>
       </c>
       <c r="E91">
-        <v>-29.62802329013573</v>
+        <v>-27.68618193632863</v>
       </c>
       <c r="F91">
-        <v>-2.594581048334813</v>
+        <v>-2.402041127799915</v>
       </c>
       <c r="G91">
-        <v>-8.99329891118381</v>
+        <v>-7.961295668750378</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.05985109537926</v>
       </c>
       <c r="E92">
-        <v>-31.10329143845855</v>
+        <v>-30.20052882384444</v>
       </c>
       <c r="F92">
-        <v>-2.366632563167251</v>
+        <v>-2.198430076926603</v>
       </c>
       <c r="G92">
-        <v>-9.253352125877603</v>
+        <v>-7.460318761054359</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.0825787370116</v>
       </c>
       <c r="E93">
-        <v>-33.36638047413278</v>
+        <v>-32.19865910956689</v>
       </c>
       <c r="F93">
-        <v>-2.590947000538732</v>
+        <v>-2.453021342870406</v>
       </c>
       <c r="G93">
-        <v>-8.850687178545666</v>
+        <v>-7.356386068158947</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.14488837625743</v>
       </c>
       <c r="E94">
-        <v>-34.52162589280754</v>
+        <v>-34.94010444009336</v>
       </c>
       <c r="F94">
-        <v>-2.524823400977664</v>
+        <v>-2.937672602491507</v>
       </c>
       <c r="G94">
-        <v>-9.276435519548295</v>
+        <v>-8.786096332147997</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.25587588544747</v>
       </c>
       <c r="E95">
-        <v>-37.58333622634149</v>
+        <v>-37.20635661486196</v>
       </c>
       <c r="F95">
-        <v>-2.462571590657281</v>
+        <v>-2.611278450073042</v>
       </c>
       <c r="G95">
-        <v>-9.518245142371574</v>
+        <v>-8.760266556032047</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.39994589187943</v>
       </c>
       <c r="E96">
-        <v>-38.63281007761909</v>
+        <v>-40.10068096365038</v>
       </c>
       <c r="F96">
-        <v>-2.648104351331897</v>
+        <v>-2.875044713370253</v>
       </c>
       <c r="G96">
-        <v>-9.271224939711898</v>
+        <v>-9.292841627345519</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.57741229443078</v>
       </c>
       <c r="E97">
-        <v>-40.39441363744691</v>
+        <v>-40.76085096143658</v>
       </c>
       <c r="F97">
-        <v>-2.4518657703435</v>
+        <v>-2.901703233127146</v>
       </c>
       <c r="G97">
-        <v>-9.706318199715826</v>
+        <v>-8.555239426890145</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.76564766654245</v>
       </c>
       <c r="E98">
-        <v>-43.54773726439303</v>
+        <v>-42.75528148389476</v>
       </c>
       <c r="F98">
-        <v>-2.696797444003258</v>
+        <v>-2.601546789824954</v>
       </c>
       <c r="G98">
-        <v>-9.987387638497861</v>
+        <v>-8.602016521441588</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.95840906014648</v>
       </c>
       <c r="E99">
-        <v>-45.46222210671979</v>
+        <v>-45.63564001884353</v>
       </c>
       <c r="F99">
-        <v>-2.654098417858555</v>
+        <v>-3.077813314594918</v>
       </c>
       <c r="G99">
-        <v>-9.719735114672396</v>
+        <v>-8.933603647352834</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.13375658691116</v>
       </c>
       <c r="E100">
-        <v>-48.03460591711791</v>
+        <v>-47.34512763555407</v>
       </c>
       <c r="F100">
-        <v>-2.6450277947979</v>
+        <v>-2.93594545645667</v>
       </c>
       <c r="G100">
-        <v>-10.52457610732391</v>
+        <v>-10.66662675107539</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.28345482783335</v>
       </c>
       <c r="E101">
-        <v>-50.28200492247407</v>
+        <v>-50.08408456961333</v>
       </c>
       <c r="F101">
-        <v>-2.802417601329806</v>
+        <v>-3.158615584533593</v>
       </c>
       <c r="G101">
-        <v>-11.04228068252998</v>
+        <v>-10.8465886287247</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.39727283340667</v>
       </c>
       <c r="E102">
-        <v>-51.74493750759999</v>
+        <v>-52.79643105828502</v>
       </c>
       <c r="F102">
-        <v>-2.935555295409951</v>
+        <v>-3.026222592748565</v>
       </c>
       <c r="G102">
-        <v>-11.05207841010648</v>
+        <v>-10.16563343727158</v>
       </c>
     </row>
   </sheetData>
